--- a/지출결의서.xlsx
+++ b/지출결의서.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Master\Desktop\새 폴더\app.py\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yju12\OneDrive\Desktop\김세희\01_업무자료\경영지원업무\01_(비즈메카) 기안서 결제\8월\260821_명함\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F3C94-E3DF-4213-98B1-16AB909799A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13140" yWindow="-16470" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="15660" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B8FE43DA-3216-4FEA-8B60-9D9D68EE4F4C}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 지출결의서" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026 지출결의서'!$A$1:$M$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026 지출결의서'!$A$1:$M$76</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>사업소명</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -101,12 +102,12 @@
     <t>단가</t>
   </si>
   <si>
-    <t>공급가액</t>
-  </si>
-  <si>
     <t>결제방법</t>
   </si>
   <si>
+    <t>송금</t>
+  </si>
+  <si>
     <t>증빙구분</t>
   </si>
   <si>
@@ -170,14 +171,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>세금계산서 - 전자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>상기와 같이 지출결의서를 작성 품의합니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2. 첨     부</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 주요내용</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -186,6 +187,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>본사</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>배송비</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -194,10 +199,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>소 계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>합 계</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -210,18 +211,91 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">  GSI  입금 요청</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>-</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">제목 : </t>
+    <t>제목 : [GSI][본사][경영지원본부] 명함 제작 건.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>김세희 사원</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>인사총무팀</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>타라그래픽스</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSI 명함</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KN 명함</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSI 명함 가변작업</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재질: 반누보 250g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재질: 스노우 250g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 사    유</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  가. 본사 주소이전에 따라 명함 제작이 필요하여 요청함.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  가. 견적서 1부.
+  나. 명함 시안 1부.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>추후별도기재</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소계</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 첨     부</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부 가 세</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  가. GSI, KN 명함 제작 건.
+  나. 제작 수량: 총 36개(GSI: 25, KN: 11)
+  다. 제작 금액: 459,800원
+  라. 계좌번호: 추후별도기재
+ </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -440,7 +514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -504,15 +578,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -553,21 +618,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -939,8 +989,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M77"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627A14AE-7C7F-41D5-9DF0-BF977576B52D}">
+  <dimension ref="B1:M78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -962,17 +1012,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -986,18 +1036,18 @@
       <c r="L2" s="19"/>
     </row>
     <row r="3" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="25" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -1005,126 +1055,134 @@
       </c>
     </row>
     <row r="4" spans="2:13" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="26"/>
+      <c r="B5" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
     </row>
     <row r="6" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="27">
+      <c r="C6" s="22"/>
+      <c r="D6" s="24">
         <f ca="1">TODAY()</f>
-        <v>46289</v>
-      </c>
-      <c r="E6" s="27"/>
+        <v>46255</v>
+      </c>
+      <c r="E6" s="24"/>
       <c r="F6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="G6" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="25"/>
       <c r="I6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
+      <c r="J6" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="34">
+      <c r="C7" s="22"/>
+      <c r="D7" s="31">
         <f ca="1">D6</f>
-        <v>46289</v>
-      </c>
-      <c r="E7" s="34"/>
+        <v>46255</v>
+      </c>
+      <c r="E7" s="31"/>
       <c r="F7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="G7" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="25"/>
       <c r="I7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
+      <c r="J7" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="35" t="str">
+      <c r="E8" s="32" t="str">
         <f>NUMBERSTRING(I8, 1) &amp; "원 정"</f>
-        <v>영원 정</v>
-      </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="37">
+        <v>사십오만구천팔백원 정</v>
+      </c>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="34">
         <f>I63</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
+        <v>459800</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
     </row>
     <row r="9" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
+      <c r="B9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
     </row>
     <row r="10" spans="2:13" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1135,86 +1193,126 @@
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="22"/>
     </row>
     <row r="11" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="8">
         <f>IF(C11="","",ROW()-10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="39"/>
+        <v>1</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="20">
+        <v>25</v>
+      </c>
+      <c r="H11" s="10">
+        <v>12000</v>
+      </c>
+      <c r="I11" s="15">
+        <v>5000</v>
+      </c>
+      <c r="J11" s="15">
+        <f>(G11*H11)+I11</f>
+        <v>305000</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="26"/>
     </row>
     <row r="12" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
+        <f>IF(C12="","",ROW()-10)</f>
         <v>2</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="22"/>
+      <c r="C12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="20">
+        <v>25</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12:J13" si="0">(G12*H12)+I12</f>
+        <v>25000</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="26"/>
     </row>
     <row r="13" spans="2:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="str">
+      <c r="B13" s="8">
         <f>IF(C13="","",ROW()-10)</f>
-        <v/>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="29"/>
+        <v>3</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="20">
+        <v>11</v>
+      </c>
+      <c r="H13" s="10">
+        <v>8000</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>88000</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="26"/>
     </row>
     <row r="14" spans="2:13" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
         <v>2</v>
       </c>
-      <c r="C14" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="C14" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>36</v>
@@ -1222,28 +1320,28 @@
       <c r="J14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="29"/>
+      <c r="L14" s="26"/>
     </row>
     <row r="15" spans="2:13" ht="49.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="8">
         <v>3</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
+      <c r="C15" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>36</v>
@@ -1251,976 +1349,988 @@
       <c r="J15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="29"/>
+      <c r="L15" s="26"/>
     </row>
     <row r="16" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="str">
-        <f t="shared" ref="B16:B61" si="0">IF(C16="","",ROW()-10)</f>
-        <v/>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
+        <f t="shared" ref="B16:B61" si="1">IF(C16="","",ROW()-10)</f>
+        <v/>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="9"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12" t="str">
-        <f t="shared" ref="I16:I61" si="1">IF(H16="","",SUM(G16*H16))</f>
+        <f t="shared" ref="I16:I61" si="2">IF(H16="","",SUM(G16*H16))</f>
         <v/>
       </c>
       <c r="J16" s="12"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
     </row>
     <row r="17" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J17" s="12"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
     </row>
     <row r="18" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
       <c r="F18" s="9"/>
       <c r="G18" s="10"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J18" s="12"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
     </row>
     <row r="19" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="9"/>
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
       <c r="I19" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J19" s="12"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
     </row>
     <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="9"/>
       <c r="G20" s="10"/>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J20" s="12"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
     </row>
     <row r="21" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="9"/>
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
       <c r="I21" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J21" s="12"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="9"/>
       <c r="G22" s="10"/>
       <c r="H22" s="11"/>
       <c r="I22" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J22" s="12"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
     </row>
     <row r="23" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="9"/>
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J23" s="12"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
     </row>
     <row r="24" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
       <c r="F24" s="9"/>
       <c r="G24" s="10"/>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J24" s="12"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
     </row>
     <row r="25" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="9"/>
       <c r="G25" s="13"/>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J25" s="12"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
     </row>
     <row r="26" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="9"/>
       <c r="G26" s="13"/>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
     </row>
     <row r="27" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="9"/>
       <c r="G27" s="14"/>
       <c r="H27" s="11"/>
       <c r="I27" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J27" s="12"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
     </row>
     <row r="28" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="9"/>
       <c r="G28" s="14"/>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J28" s="12"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
     <row r="29" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
       <c r="F29" s="9"/>
       <c r="G29" s="14"/>
       <c r="H29" s="11"/>
       <c r="I29" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J29" s="12"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
       <c r="F30" s="9"/>
       <c r="G30" s="14"/>
       <c r="H30" s="11"/>
       <c r="I30" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J30" s="12"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
     </row>
     <row r="31" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
       <c r="F31" s="9"/>
       <c r="G31" s="14"/>
       <c r="H31" s="11"/>
       <c r="I31" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J31" s="12"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
     <row r="32" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
       <c r="F32" s="9"/>
       <c r="G32" s="14"/>
       <c r="H32" s="11"/>
       <c r="I32" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J32" s="12"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
     </row>
     <row r="33" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
       <c r="F33" s="9"/>
       <c r="G33" s="14"/>
       <c r="H33" s="11"/>
       <c r="I33" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J33" s="12"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
     </row>
     <row r="34" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
       <c r="F34" s="9"/>
       <c r="G34" s="14"/>
       <c r="H34" s="11"/>
       <c r="I34" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J34" s="12"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
     </row>
     <row r="35" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
       <c r="F35" s="9"/>
       <c r="G35" s="14"/>
       <c r="H35" s="11"/>
       <c r="I35" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J35" s="12"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
     <row r="36" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
       <c r="F36" s="9"/>
       <c r="G36" s="14"/>
       <c r="H36" s="11"/>
       <c r="I36" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J36" s="12"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
     </row>
     <row r="37" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
       <c r="F37" s="9"/>
       <c r="G37" s="14"/>
       <c r="H37" s="11"/>
       <c r="I37" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J37" s="12"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
       <c r="F38" s="9"/>
       <c r="G38" s="14"/>
       <c r="H38" s="11"/>
       <c r="I38" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J38" s="12"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
     </row>
     <row r="39" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
       <c r="F39" s="9"/>
       <c r="G39" s="14"/>
       <c r="H39" s="11"/>
       <c r="I39" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J39" s="12"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
     </row>
     <row r="40" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
       <c r="F40" s="9"/>
       <c r="G40" s="14"/>
       <c r="H40" s="11"/>
       <c r="I40" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J40" s="12"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
     </row>
     <row r="41" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
       <c r="F41" s="9"/>
       <c r="G41" s="14"/>
       <c r="H41" s="11"/>
       <c r="I41" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J41" s="12"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
     </row>
     <row r="42" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
       <c r="F42" s="9"/>
       <c r="G42" s="14"/>
       <c r="H42" s="11"/>
       <c r="I42" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J42" s="12"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
     </row>
     <row r="43" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
       <c r="F43" s="9"/>
       <c r="G43" s="14"/>
       <c r="H43" s="11"/>
       <c r="I43" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J43" s="12"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
     </row>
     <row r="44" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
       <c r="F44" s="9"/>
       <c r="G44" s="14"/>
       <c r="H44" s="11"/>
       <c r="I44" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J44" s="12"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
     </row>
     <row r="45" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
       <c r="F45" s="9"/>
       <c r="G45" s="14"/>
       <c r="H45" s="16"/>
       <c r="I45" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J45" s="12"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
     </row>
     <row r="46" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
       <c r="F46" s="9"/>
       <c r="G46" s="14"/>
       <c r="H46" s="16"/>
       <c r="I46" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J46" s="12"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
     </row>
     <row r="47" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
       <c r="F47" s="9"/>
       <c r="G47" s="14"/>
       <c r="H47" s="16"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J47" s="12"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
     </row>
     <row r="48" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
       <c r="F48" s="9"/>
       <c r="G48" s="14"/>
       <c r="H48" s="16"/>
       <c r="I48" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J48" s="12"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="25"/>
     </row>
     <row r="49" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
       <c r="F49" s="9"/>
       <c r="G49" s="14"/>
       <c r="H49" s="16"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J49" s="12"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="25"/>
     </row>
     <row r="50" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="9"/>
       <c r="G50" s="14"/>
       <c r="H50" s="16"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J50" s="12"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
     </row>
     <row r="51" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="9"/>
       <c r="G51" s="14"/>
       <c r="H51" s="16"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J51" s="12"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="25"/>
     </row>
     <row r="52" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
       <c r="F52" s="9"/>
       <c r="G52" s="14"/>
       <c r="H52" s="16"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J52" s="12"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="25"/>
     </row>
     <row r="53" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
       <c r="F53" s="9"/>
       <c r="G53" s="14"/>
       <c r="H53" s="16"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J53" s="12"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
     </row>
     <row r="54" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
       <c r="F54" s="9"/>
       <c r="G54" s="14"/>
       <c r="H54" s="16"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J54" s="12"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
     </row>
     <row r="55" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
       <c r="F55" s="9"/>
       <c r="G55" s="14"/>
       <c r="H55" s="16"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J55" s="12"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
     </row>
     <row r="56" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
       <c r="F56" s="9"/>
       <c r="G56" s="14"/>
       <c r="H56" s="16"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J56" s="12"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
     </row>
     <row r="57" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
       <c r="F57" s="9"/>
       <c r="G57" s="14"/>
       <c r="H57" s="16"/>
       <c r="I57" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J57" s="12"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
     </row>
     <row r="58" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
       <c r="F58" s="9"/>
       <c r="G58" s="14"/>
       <c r="H58" s="16"/>
       <c r="I58" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J58" s="12"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
     </row>
     <row r="59" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
       <c r="F59" s="9"/>
       <c r="G59" s="14"/>
       <c r="H59" s="16"/>
       <c r="I59" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J59" s="12"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="25"/>
     </row>
     <row r="60" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
       <c r="F60" s="9"/>
       <c r="G60" s="14"/>
       <c r="H60" s="16"/>
       <c r="I60" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J60" s="12"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-    </row>
-    <row r="61" spans="2:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K60" s="25"/>
+      <c r="L60" s="25"/>
+    </row>
+    <row r="61" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
       <c r="F61" s="9"/>
       <c r="G61" s="14"/>
       <c r="H61" s="16"/>
       <c r="I61" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J61" s="12"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
     </row>
     <row r="62" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25" t="s">
+      <c r="B62" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="37">
+        <v>41800</v>
+      </c>
+      <c r="J62" s="37"/>
+      <c r="K62" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="J62" s="25"/>
-      <c r="K62" s="29" t="s">
+      <c r="L62" s="26"/>
+    </row>
+    <row r="63" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="37">
+        <f>SUM(J11:J13,I62)</f>
+        <v>459800</v>
+      </c>
+      <c r="J63" s="37"/>
+      <c r="K63" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L62" s="29"/>
-    </row>
-    <row r="63" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="45">
-        <f>SUM(H11:H15)</f>
-        <v>0</v>
-      </c>
-      <c r="J63" s="45"/>
-      <c r="K63" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="29"/>
+      <c r="L63" s="26"/>
     </row>
     <row r="64" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="25" t="s">
+      <c r="B64" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="25"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
+      <c r="E64" s="25"/>
       <c r="F64" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
+      <c r="G64" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="25"/>
     </row>
     <row r="65" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="25"/>
+      <c r="C65" s="22"/>
       <c r="D65" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="18"/>
+      <c r="E65" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="F65" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
+      <c r="G65" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
       <c r="J65" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K65" s="28"/>
-      <c r="L65" s="28"/>
+      <c r="K65" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="L65" s="25"/>
     </row>
     <row r="66" spans="2:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
-      <c r="L66" s="49"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="41"/>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="3"/>
@@ -2236,19 +2346,19 @@
       <c r="L67" s="3"/>
     </row>
     <row r="68" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="50"/>
-      <c r="D68" s="50"/>
-      <c r="E68" s="50"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
-      <c r="H68" s="50"/>
-      <c r="I68" s="50"/>
-      <c r="J68" s="50"/>
-      <c r="K68" s="50"/>
-      <c r="L68" s="50"/>
+      <c r="B68" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
+      <c r="L68" s="42"/>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="3"/>
@@ -2264,120 +2374,133 @@
       <c r="L69" s="3"/>
     </row>
     <row r="70" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="50" t="s">
+      <c r="B70" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="50"/>
-    </row>
-    <row r="71" spans="2:12" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="44"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="23"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-    </row>
-    <row r="73" spans="2:12" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="50"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="50"/>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="50"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B74" s="44"/>
-      <c r="C74" s="44"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="44"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="44"/>
-      <c r="I74" s="44"/>
-      <c r="J74" s="44"/>
-      <c r="K74" s="44"/>
-      <c r="L74" s="44"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="L70" s="42"/>
+    </row>
+    <row r="71" spans="2:12" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="36"/>
+    </row>
+    <row r="72" spans="2:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B72" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
+      <c r="L72" s="42"/>
+    </row>
+    <row r="73" spans="2:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="36"/>
+    </row>
+    <row r="74" spans="2:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B74" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" s="42"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
+      <c r="L74" s="42"/>
+    </row>
+    <row r="75" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
+      <c r="K75" s="36"/>
+      <c r="L75" s="36"/>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B76" s="44" t="s">
+      <c r="B76" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="44"/>
-      <c r="D76" s="44"/>
-      <c r="E76" s="44"/>
-      <c r="F76" s="44"/>
-      <c r="G76" s="44"/>
-      <c r="H76" s="44"/>
-      <c r="I76" s="44"/>
-      <c r="J76" s="44"/>
-      <c r="K76" s="44"/>
-      <c r="L76" s="44"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
+      <c r="L76" s="36"/>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
-      <c r="K77" s="24"/>
-      <c r="L77" s="24"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
+      <c r="L78" s="21"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="qAAaSxdcCzritEHx0hkNzh7ZaZyVQqWmLOZaL5KHN1tPPyKYC4GBNwuEL6WsbdcGxo4oCjOfoWY6dgIuDdT6kA==" saltValue="uGmcMPPduR93sptcPrrfaA==" spinCount="100000" sqref="J2 L2" name="범위1"/>
   </protectedRanges>
-  <mergeCells count="143">
+  <mergeCells count="144">
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B73:L73"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="K57:L57"/>
     <mergeCell ref="C58:E58"/>
@@ -2409,8 +2532,8 @@
     <mergeCell ref="B68:L68"/>
     <mergeCell ref="B70:L70"/>
     <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B73:L73"/>
     <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B75:L75"/>
     <mergeCell ref="B63:H63"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="I62:J62"/>
@@ -2494,13 +2617,12 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="K11:L11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B75:L75"/>
     <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="B6:C6"/>
@@ -2524,7 +2646,7 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="J2:L2">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="J2:L2" xr:uid="{C71CB713-F178-4914-A531-85C254662195}">
       <formula1>"마지막 업데이트: 2025-02-07"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2534,93 +2656,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425B4AC4-3D5C-4891-B04B-A518D1D1BEA1}">
   <dimension ref="B2:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="3" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
     </row>
     <row r="4" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
     </row>
     <row r="6" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
     </row>
     <row r="7" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
     </row>
     <row r="9" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
     </row>
     <row r="10" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
     </row>
     <row r="11" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
     </row>
     <row r="12" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
     </row>
     <row r="13" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="12">
